--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1349,155 +1349,222 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="13" ht="140" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>令和8年9月15日　生活実態反映版</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>R8.9.15</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>調査結果の本文反映</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査（4,729票）の結果を第2章第4節に反映した。同節は4段落・表1のみであったものを30段落・表8とした。①調査の対象者の範囲（要支援者・要介護者を含まないこと、他の調査と合算しないこと）を明記した。②主要指標の町別、年齢調整後の町間の差の検定（有意7項目・有意でない4項目）を掲げた。③同規模保険者40との比較（課題5・同等1）を掲げた。④社会参加及び暮らし向きとの関連を掲げた（フレイル該当割合は暮らし向きが大変苦しい層42.7％に対し大変ゆとりがある層6.8％）。⑤地区の定義（小学校区とするか）は［要確認］のまま残した。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>調査クロス集計・分析（24シート）、健康とくらしの調査の集計値（個票は収録しない）</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>第2章第4節</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="140" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>令和8年9月16日　見込量反映版</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>R8.9.16</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>見込量・給付費・保険料の反映</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定 第1次概算（18シート）の結果を本文に反映した。本文の数値は算定のスクリプトから引いており、固定値を書き写していない。①第6章第1節に要介護度別の認定者数の表を加えた（年齢階級ごとの要介護度の構成を令和7年度末で固定し、年齢階級別認定者数に乗じたもの。合計は認定者数と一致する）。②第6章第2節の見込量を、見える化システムの自然体推計値から令和7年度の年報（要介護度別・広域連合単位）を基準とする受託者の算定に置き換えた。表頭の「R8実績」を「R7実績」に改めた。③同節に（4）利用回（日）数を加えた（介護保険法第117条第2項第1号の記載事項）。④同節2の介護予防給付サービスを要支援1・2の内訳により掲げた（従前は介護給付との内訳が確定できないとしていたもの）。⑤第6章第3節1の給付費を要介護度別の算定に置き換えた。基準年度では見える化システムの総括表詳細を円単位で再現する。⑥同節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを加えた（同項第2号の記載事項）。⑦同節3の総給付費等を算定の値に改め、令和17年度・令和22年度の総給付費を加えた。⑧第6章第6節の暫定算定を月額6,740円から6,436円に改め、給付費の置き方によるちがい（要介護度別・一律・見える化）を加えた。前提を動かした場合の幅に介護報酬改定率を加えた。⑨第6章第6節4の保険料算定表に記号A〜Jの年度別の額を入れた（従前は「―」であったもの）。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定 第1次概算（18シート・自己点検22件）、年報（令和7年度）の要介護度別明細、将来推計 第1段階（人口と認定者数）・第3段階（給付費と保険料）</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>第6章第1節
+第6章第2節
+第6章第3節
+第6章第6節</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>【本素案の取扱い（巻末の段落から移動）】</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="76" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>本書は、第9期計画の章立てと体裁を踏襲しつつ、第10期の国の検討方向、第9期の課題評価、構成3町の高齢者福祉計画、及び地域包括ケア「見える化」システムのデータによる妥当性検証を反映したものである。第2章にサービス提供体制の節、第3章に交付金評価の節を新設し、第5章をロジックモデルの5層構成に改めた。代表KPIのデータ源を指標ごとに確定した。事業所調査、供給制約、制度改正等が未確定の箇所は、確定値を推測せず［要内訳］［要確認］又は［要協議］としている。</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="8" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>【今後の版の予定】</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>予定時期</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>反映する内容</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>前提となる確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>協議用素案（令和8年9月時点）</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>03シートA1〜A22
-04シートB1〜B28</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>計画骨子案</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>計画素案（提出版）</t>
+          <t>協議用素案（令和8年9月時点）</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
+          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="8" t="n"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+          <t>03シートA1〜A22
+04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>計画最終案</t>
+          <t>計画骨子案</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの結果を反映する。</t>
+          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="5" t="inlineStr">
         <is>
+          <t>資料提供依頼No.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>計画素案（提出版）</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>計画最終案</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの結果を反映する。</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）版の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）令和8年7月29日の是正内容の詳細は、受託者の自己点検及び受託者の自己点検に記載している。</t>
         </is>
@@ -1505,15 +1572,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="C22:E22"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1416,155 +1416,230 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="15" ht="140" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>令和8年9月24日　調査所見反映版</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>R8.9.24</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>実施済み調査の所見の反映</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>アンケート調査の集計分析報告書の所見のうち、取扱いの決定を要しないものを本文に反映した。①第1章第7節に通常の事業の実施地域による確認（訪問系・通所系5サービスの町別のカバー）を加えた。②第2章第3節に運営法人の状況（実75事業所を28法人が運営し、上位6法人が39事業所＝52.0％）を加えた。③第6章第4節に区域内の入居状況と当広域連合の被保険者の受給者数の対照及び供給の担い手の集中を加えた。定員に対する当連合の被保険者の受給者数の割合が低いことは区域内に空きがあることを意味しないことを明記した。④第6章第5節に入所の経路からみた整備の考え方（新規入所の57.0％・退去先の47.0％が病院・診療所）を加えた。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>アンケート調査の集計分析報告書（15シート）、実施済み調査 結果報告書、北海道の指定事業所一覧</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>第1章第7節
+第2章第3節
+第2章第6節
+第6章第4節
+第6章第5節</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="140" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>令和8年9月25日　整合是正・認知症施策反映版</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>R8.9.25</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>指標の整合の是正と認知症施策の実施状況の反映</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>①代表KPI16項目の名称・定義・算式・基準値を1か所にまとめ、第5章第3節・各基本目標の達成目標・資料1が同じ定義を掲げる形に改めた（従前は当初の定義と代理指標の定義が併存していた）。②在宅生活改善調査による基準値の分母を設問ごとの有効回答に改めた（在宅生活の維持の見通し 72÷98＝73.5％、区域内で提供できないサービスが必要と判断された利用者の割合 20÷99＝20.2％）。③通いの場参加率（総合事業ベース）を第5章 基本目標2でも令和6年度3.53％に統一した。④特定施設の入居率を施設別（98.3％・97.0％）に改め、時点の異なる合計は参考値と明記した。⑤第2章第2節5の町別の給付費の注を、3町のファイルの合計と広域連合単位のファイルが要介護度ごとに一致することに改めた。⑥第6章第3節2の地域支援事業の量の出典を総合事業の実施状況に関する調査に改めた。⑦第5章 基本目標2に認知症初期集中支援推進事業の実施状況を加えた（構成3町が担当チームを設置しているが、令和7年度は美瑛町が対応件数0件で医師を確保できず休止している）。施策の方向性に体制の確認と再開の見通しの整理を、主な事業の目標に稼働している町数を加えた。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>アンケート調査の集計分析報告書（15シート・自己点検11件）、在宅生活改善調査による代表KPIの基準値、給付費データ集計（令和7年度の再提供分）、地域包括支援センター事業実施報告書（構成3町）</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節
+第2章第3節
+第2章第4節
+第5章第3節
+第5章 基本目標2・4
+第6章第3節
+第6章第4節
+資料1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>【本素案の取扱い（巻末の段落から移動）】</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>本書は、第9期計画の章立てと体裁を踏襲しつつ、第10期の国の検討方向、第9期の課題評価、構成3町の高齢者福祉計画、及び地域包括ケア「見える化」システムのデータによる妥当性検証を反映したものである。第2章にサービス提供体制の節、第3章に交付金評価の節を新設し、第5章をロジックモデルの5層構成に改めた。代表KPIのデータ源を指標ごとに確定した。事業所調査、供給制約、制度改正等が未確定の箇所は、確定値を推測せず［要内訳］［要確認］又は［要協議］としている。</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="8" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>【今後の版の予定】</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>予定時期</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>反映する内容</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>前提となる確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>協議用素案（令和8年9月時点）</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>03シートA1〜A22
-04シートB1〜B28</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>計画骨子案</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>計画素案（提出版）</t>
+          <t>協議用素案（令和8年9月時点）</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
+          <t>本表03・04シートの確認事項の決定内容を反映する。健康とくらしの調査の分析結果（調査クロス集計・分析24シート）を第2章第4節・第5章基本目標1へ反映する。</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="8" t="n"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+          <t>03シートA1〜A22
+04シートB1〜B28</t>
         </is>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>計画最終案</t>
+          <t>計画骨子案</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>R9.2</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>パブリックコメントの結果を反映する。</t>
+          <t>策定委員会での意見を反映する。第9期の事業実績（令和6〜8年度）によるプロセス評価を第3章へ反映する。</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
+          <t>資料提供依頼No.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>計画素案（提出版）</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の確定値、保険料の試算、施設整備方針を反映する。</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="8" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.6・No.7・No.9・No.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>計画最終案</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>R9.2</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの結果を反映する。</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>―</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="96" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="28" ht="96" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>注1）第9期計画の表紙及び巻末には変更履歴の記載がない。計画は完成した文書として住民・委員に示すものであり、作成の過程は本表で管理する。注2）版の履歴は、成果品の納品時に発注者へ本表として提出する。計画本文（Word）には含めない。注3）令和8年7月29日の是正内容の詳細は、受託者の自己点検及び受託者の自己点検に記載している。</t>
         </is>
@@ -1573,13 +1648,13 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="C25:E25"/>
     <mergeCell ref="C24:E24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -4845,7 +4845,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>採用パターンをどちらに置くか。サービス見込量 第1次概算（9月26日）より前に決定を要する。</t>
+          <t>採用パターンをどちらに置くか。サービス見込量の算定（9月26日）より前に決定を要する。</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">

--- a/output/第10期計画_計画素案の別管理表.xlsx
+++ b/output/第10期計画_計画素案の別管理表.xlsx
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>①代表KPI16項目の名称・定義・算式・基準値を1か所にまとめ、第5章第3節・各基本目標の達成目標・資料1が同じ定義を掲げる形に改めた（従前は当初の定義と代理指標の定義が併存していた）。②在宅生活改善調査による基準値の分母を設問ごとの有効回答に改めた（在宅生活の維持の見通し 72÷98＝73.5％、区域内で提供できないサービスが必要と判断された利用者の割合 20÷99＝20.2％）。③通いの場参加率（総合事業ベース）を第5章 基本目標2でも令和6年度3.53％に統一した。④特定施設の入居率を施設別（98.3％・97.0％）に改め、時点の異なる合計は参考値と明記した。⑤第2章第2節5の町別の給付費の注を、3町のファイルの合計と広域連合単位のファイルが要介護度ごとに一致することに改めた。⑥第6章第3節2の地域支援事業の量の出典を総合事業の実施状況に関する調査に改めた。⑦第5章 基本目標2に認知症初期集中支援推進事業の実施状況を加えた（構成3町が担当チームを設置しているが、令和7年度は美瑛町が対応件数0件で医師を確保できず休止している）。施策の方向性に体制の確認と再開の見通しの整理を、主な事業の目標に稼働している町数を加えた。</t>
+          <t>①代表KPI16項目の名称・定義・算式・基準値を1か所にまとめ、第4章第3節・各基本目標の達成目標・資料1が同じ定義を掲げる形に改めた（従前は当初の定義と代理指標の定義が併存していた）。②在宅生活改善調査による基準値の分母を設問ごとの有効回答に改めた（在宅生活の維持の見通し 72÷98＝73.5％、区域内で提供できないサービスが必要と判断された利用者の割合 20÷99＝20.2％）。③通いの場参加率（総合事業ベース）を第5章 基本目標2でも令和6年度3.53％に統一した。④特定施設の入居率を施設別（98.3％・97.0％）に改め、時点の異なる合計は参考値と明記した。⑤第2章第2節5の町別の給付費の注を、3町のファイルの合計と広域連合単位のファイルが要介護度ごとに一致することに改めた。⑥第6章第3節2の地域支援事業の量の出典を総合事業の実施状況に関する調査に改めた。⑦第5章 基本目標2に認知症初期集中支援推進事業の実施状況を加えた（構成3町が担当チームを設置しているが、令和7年度は美瑛町が対応件数0件で医師を確保できず休止している）。施策の方向性に体制の確認と再開の見通しの整理を、主な事業の目標に稼働している町数を加えた。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1483,7 +1483,7 @@
           <t>第2章第2節
 第2章第3節
 第2章第4節
-第5章第3節
+第4章第3節
 第5章 基本目標2・4
 第6章第3節
 第6章第4節
